--- a/calendar.xlsx
+++ b/calendar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/corrado/_repositories/psicometria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89FF309F-41C2-A64A-B52D-C77D2A9F487C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA38B69-ECC2-4A47-A687-B412D05B9055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="19140" windowHeight="17040" xr2:uid="{872AAEF1-18A8-4E48-A75A-35689B2506A9}"/>
+    <workbookView xWindow="10740" yWindow="500" windowWidth="19140" windowHeight="17040" xr2:uid="{872AAEF1-18A8-4E48-A75A-35689B2506A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -141,9 +141,6 @@
     <t>31, 32, 33, 34</t>
   </si>
   <si>
-    <t>28, 29, 30</t>
-  </si>
-  <si>
     <t>1, 2, 3, 4, 5</t>
   </si>
   <si>
@@ -154,6 +151,9 @@
   </si>
   <si>
     <t>14, 15, 16, 17</t>
+  </si>
+  <si>
+    <t>27, 28, 29, 30</t>
   </si>
 </sst>
 </file>
@@ -525,7 +525,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -539,7 +539,7 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -553,7 +553,7 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -567,7 +567,7 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -634,7 +634,7 @@
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
